--- a/Himanshi_Sangani_ExcelDashboard.xlsx
+++ b/Himanshi_Sangani_ExcelDashboard.xlsx
@@ -8,30 +8,29 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\All_Project_Data\EXCEL_PROJECTS\Pratical_Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FA1D02C-3AF6-448B-B531-D78E0D1A199C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C44715AC-39C8-4AEB-834E-8CCDCBED7590}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{7C897265-1BC0-4F33-A939-F1C668D85C3C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{7C897265-1BC0-4F33-A939-F1C668D85C3C}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard " sheetId="4" r:id="rId1"/>
     <sheet name="Analysis" sheetId="1" r:id="rId2"/>
-    <sheet name="Summery Report" sheetId="5" r:id="rId3"/>
-    <sheet name="Pivot Tables" sheetId="3" r:id="rId4"/>
-    <sheet name="Book Transction" sheetId="2" r:id="rId5"/>
+    <sheet name="Pivot Tables" sheetId="3" r:id="rId3"/>
+    <sheet name="Book Transction" sheetId="2" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="ExternalData_1" localSheetId="4" hidden="1">'Book Transction'!$A$1:$L$121</definedName>
+    <definedName name="ExternalData_1" localSheetId="3" hidden="1">'Book Transction'!$A$1:$L$121</definedName>
     <definedName name="NativeTimeline_Issue_Date">#N/A</definedName>
     <definedName name="Slicer_Department">#N/A</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId6"/>
+    <pivotCache cacheId="0" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
       <x14:slicerCaches>
-        <x14:slicerCache r:id="rId7"/>
+        <x14:slicerCache r:id="rId6"/>
       </x14:slicerCaches>
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
@@ -39,7 +38,7 @@
     </ext>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}">
       <x15:timelineCacheRefs>
-        <x15:timelineCacheRef r:id="rId8"/>
+        <x15:timelineCacheRef r:id="rId7"/>
       </x15:timelineCacheRefs>
     </ext>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -2232,10 +2231,10 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>0.30769230769230771</c:v>
+                  <c:v>0.27272727272727271</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.69230769230769229</c:v>
+                  <c:v>0.72727272727272729</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2678,9 +2677,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Pivot Tables'!$D$8:$D$20</c:f>
+              <c:f>'Pivot Tables'!$D$8:$D$18</c:f>
               <c:strCache>
-                <c:ptCount val="13"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>5008</c:v>
                 </c:pt>
@@ -2712,23 +2711,17 @@
                   <c:v>5059</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>5069</c:v>
-                </c:pt>
-                <c:pt idx="11">
                   <c:v>5073</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>5083</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Pivot Tables'!$E$8:$E$20</c:f>
+              <c:f>'Pivot Tables'!$E$8:$E$18</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
-                <c:ptCount val="13"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -2760,12 +2753,6 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="12">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -3492,7 +3479,7 @@
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>3</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>3</c:v>
@@ -3501,7 +3488,7 @@
                   <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4090,10 +4077,10 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>0.69230769230769229</c:v>
+                  <c:v>0.72727272727272729</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.30769230769230771</c:v>
+                  <c:v>0.27272727272727271</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4592,13 +4579,13 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>1</c:v>
@@ -5062,13 +5049,13 @@
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>4</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>2</c:v>
@@ -13657,12 +13644,12 @@
   </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <filters count="1">
-    <filter fld="9" type="dateBetween" evalOrder="-1" id="120" name="Issue Date">
+    <filter fld="9" type="dateBetween" evalOrder="-1" id="127" name="Issue Date">
       <autoFilter ref="A1">
         <filterColumn colId="0">
           <customFilters and="1">
             <customFilter operator="greaterThanOrEqual" val="46023"/>
-            <customFilter operator="lessThanOrEqual" val="46203"/>
+            <customFilter operator="lessThanOrEqual" val="46173"/>
           </customFilters>
         </filterColumn>
       </autoFilter>
@@ -13686,7 +13673,7 @@
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6E710BE7-FE6E-4CEF-93FB-02D53D7A37E4}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3" rowHeaderCaption="Transction ">
-  <location ref="D7:E20" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <location ref="D7:E18" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField axis="axisRow" showAll="0">
       <items count="121">
@@ -14036,7 +14023,7 @@
   <rowFields count="1">
     <field x="0"/>
   </rowFields>
-  <rowItems count="13">
+  <rowItems count="11">
     <i>
       <x v="7"/>
     </i>
@@ -14068,13 +14055,7 @@
       <x v="58"/>
     </i>
     <i>
-      <x v="68"/>
-    </i>
-    <i>
       <x v="72"/>
-    </i>
-    <i>
-      <x v="82"/>
     </i>
   </rowItems>
   <colItems count="1">
@@ -14153,12 +14134,12 @@
   </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <filters count="1">
-    <filter fld="9" type="dateBetween" evalOrder="-1" id="131" name="Issue Date">
+    <filter fld="9" type="dateBetween" evalOrder="-1" id="138" name="Issue Date">
       <autoFilter ref="A1">
         <filterColumn colId="0">
           <customFilters and="1">
             <customFilter operator="greaterThanOrEqual" val="46023"/>
-            <customFilter operator="lessThanOrEqual" val="46203"/>
+            <customFilter operator="lessThanOrEqual" val="46173"/>
           </customFilters>
         </filterColumn>
       </autoFilter>
@@ -14468,12 +14449,12 @@
   </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <filters count="1">
-    <filter fld="9" type="dateBetween" evalOrder="-1" id="120" name="Issue Date">
+    <filter fld="9" type="dateBetween" evalOrder="-1" id="127" name="Issue Date">
       <autoFilter ref="A1">
         <filterColumn colId="0">
           <customFilters and="1">
             <customFilter operator="greaterThanOrEqual" val="46023"/>
-            <customFilter operator="lessThanOrEqual" val="46203"/>
+            <customFilter operator="lessThanOrEqual" val="46173"/>
           </customFilters>
         </filterColumn>
       </autoFilter>
@@ -14777,12 +14758,12 @@
   </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <filters count="1">
-    <filter fld="9" type="dateBetween" evalOrder="-1" id="120" name="Issue Date">
+    <filter fld="9" type="dateBetween" evalOrder="-1" id="127" name="Issue Date">
       <autoFilter ref="A1">
         <filterColumn colId="0">
           <customFilters and="1">
             <customFilter operator="greaterThanOrEqual" val="46023"/>
-            <customFilter operator="lessThanOrEqual" val="46203"/>
+            <customFilter operator="lessThanOrEqual" val="46173"/>
           </customFilters>
         </filterColumn>
       </autoFilter>
@@ -15047,12 +15028,12 @@
   </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <filters count="1">
-    <filter fld="9" type="dateBetween" evalOrder="-1" id="120" name="Issue Date">
+    <filter fld="9" type="dateBetween" evalOrder="-1" id="127" name="Issue Date">
       <autoFilter ref="A1">
         <filterColumn colId="0">
           <customFilters and="1">
             <customFilter operator="greaterThanOrEqual" val="46023"/>
-            <customFilter operator="lessThanOrEqual" val="46203"/>
+            <customFilter operator="lessThanOrEqual" val="46173"/>
           </customFilters>
         </filterColumn>
       </autoFilter>
@@ -15439,12 +15420,12 @@
   </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <filters count="1">
-    <filter fld="9" type="dateBetween" evalOrder="-1" id="120" name="Issue Date">
+    <filter fld="9" type="dateBetween" evalOrder="-1" id="127" name="Issue Date">
       <autoFilter ref="A1">
         <filterColumn colId="0">
           <customFilters and="1">
             <customFilter operator="greaterThanOrEqual" val="46023"/>
-            <customFilter operator="lessThanOrEqual" val="46203"/>
+            <customFilter operator="lessThanOrEqual" val="46173"/>
           </customFilters>
         </filterColumn>
       </autoFilter>
@@ -15933,7 +15914,7 @@
     <pivotTable tabId="3" name="PivotTable9"/>
   </pivotTables>
   <state minimalRefreshVersion="6" lastRefreshVersion="6" pivotCacheId="749344393" filterType="dateBetween">
-    <selection startDate="2026-01-01T00:00:00" endDate="2026-06-30T00:00:00"/>
+    <selection startDate="2026-01-01T00:00:00" endDate="2026-05-31T00:00:00"/>
     <bounds startDate="2026-01-01T00:00:00" endDate="2027-01-01T00:00:00"/>
   </state>
 </timelineCacheDefinition>
@@ -15941,7 +15922,7 @@
 
 <file path=xl/timelines/timeline1.xml><?xml version="1.0" encoding="utf-8"?>
 <timelines xmlns="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
-  <timeline name="Issue Date" xr10:uid="{EEDF185E-DFF8-4021-8EA7-667DCF972CAE}" cache="NativeTimeline_Issue_Date" caption="Issue Date" showHeader="0" showSelectionLabel="0" showTimeLevel="0" level="2" selectionLevel="1" scrollPosition="2026-01-01T00:00:00" style="TimeSlicerStyleLight5 2"/>
+  <timeline name="Issue Date" xr10:uid="{EEDF185E-DFF8-4021-8EA7-667DCF972CAE}" cache="NativeTimeline_Issue_Date" caption="Issue Date" showHeader="0" showSelectionLabel="0" showTimeLevel="0" level="2" selectionLevel="2" scrollPosition="2026-01-01T00:00:00" style="TimeSlicerStyleLight5 2"/>
 </timelines>
 </file>
 
@@ -16833,15 +16814,6 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6B2B7FF-C26B-44B2-B5A1-A4EC4610D572}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27A59C36-7F73-468F-BA83-B3482956DB46}">
   <dimension ref="A2:M20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -16891,19 +16863,19 @@
         <v>27</v>
       </c>
       <c r="E3" s="15">
-        <v>0.30769230769230771</v>
+        <v>0.27272727272727271</v>
       </c>
       <c r="H3" s="16" t="s">
         <v>79</v>
       </c>
       <c r="I3" s="12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L3" s="14" t="s">
         <v>52</v>
       </c>
       <c r="M3" s="12">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
@@ -16911,7 +16883,7 @@
         <v>16</v>
       </c>
       <c r="E4" s="15">
-        <v>0.69230769230769229</v>
+        <v>0.72727272727272729</v>
       </c>
       <c r="H4" s="16" t="s">
         <v>87</v>
@@ -16937,7 +16909,7 @@
         <v>86</v>
       </c>
       <c r="M5" s="12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
@@ -16948,7 +16920,7 @@
         <v>48</v>
       </c>
       <c r="I6" s="12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L6" s="14" t="s">
         <v>25</v>
@@ -17095,13 +17067,13 @@
         <v>50</v>
       </c>
       <c r="I15" s="12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L15" s="14" t="s">
         <v>102</v>
       </c>
       <c r="M15" s="15">
-        <v>0.69230769230769229</v>
+        <v>0.72727272727272729</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
@@ -17121,7 +17093,7 @@
         <v>94</v>
       </c>
       <c r="M16" s="15">
-        <v>0.30769230769230771</v>
+        <v>0.27272727272727271</v>
       </c>
     </row>
     <row r="17" spans="4:9" x14ac:dyDescent="0.25">
@@ -17135,12 +17107,12 @@
         <v>84</v>
       </c>
       <c r="I17" s="12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D18" s="16">
-        <v>5069</v>
+        <v>5073</v>
       </c>
       <c r="E18" s="12">
         <v>1</v>
@@ -17153,12 +17125,6 @@
       </c>
     </row>
     <row r="19" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D19" s="16">
-        <v>5073</v>
-      </c>
-      <c r="E19" s="12">
-        <v>1</v>
-      </c>
       <c r="H19" s="16" t="s">
         <v>77</v>
       </c>
@@ -17167,12 +17133,6 @@
       </c>
     </row>
     <row r="20" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D20" s="16">
-        <v>5083</v>
-      </c>
-      <c r="E20" s="12">
-        <v>1</v>
-      </c>
       <c r="H20" s="16" t="s">
         <v>23</v>
       </c>
@@ -17185,7 +17145,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB6A1C63-E27B-4E43-8C83-D1974D6D2222}">
   <dimension ref="A1:O121"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
